--- a/src/assets/template/De-Book Template.xlsx
+++ b/src/assets/template/De-Book Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qyuan4\OneDrive - DXC Production\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GAVIN\PRO_Philips\code_repository\COS-UI\src\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1769060B-3614-4A5E-B387-AAEF0C42A02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8C864F-8D32-400B-9775-F95144FDFBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{508F1C01-1DFE-48B5-B5B8-EF954143378D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{508F1C01-1DFE-48B5-B5B8-EF954143378D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -48,49 +48,49 @@
   <commentList>
     <comment ref="E1" authorId="0" shapeId="0" xr:uid="{4B9CCD89-3C59-4D3B-A63C-7C9469034ED7}">
       <text>
-        <t>[线程批注]
-你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
-注释:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     add per requested</t>
       </text>
     </comment>
     <comment ref="F1" authorId="1" shapeId="0" xr:uid="{CFA3A8E2-754B-416A-A7C8-AF3123814806}">
       <text>
-        <t>[线程批注]
-你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
-注释:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     add per requested</t>
       </text>
     </comment>
     <comment ref="H1" authorId="2" shapeId="0" xr:uid="{486F323A-57E4-40DD-AAB4-27B611FE59B7}">
       <text>
-        <t>[线程批注]
-你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
-注释:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     new add</t>
       </text>
     </comment>
     <comment ref="I1" authorId="3" shapeId="0" xr:uid="{22BB3238-075E-4CA5-882B-5647914FB99B}">
       <text>
-        <t>[线程批注]
-你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
-注释:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     new add</t>
       </text>
     </comment>
     <comment ref="J1" authorId="4" shapeId="0" xr:uid="{E8557E5F-4FFD-4EE1-9229-3FFE2B8052C3}">
       <text>
-        <t>[线程批注]
-你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
-注释:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     new added</t>
       </text>
     </comment>
     <comment ref="K1" authorId="5" shapeId="0" xr:uid="{3572AC16-435B-42E2-A14D-CBC563FC5795}">
       <text>
-        <t>[线程批注]
-你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
-注释:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     new added</t>
       </text>
     </comment>
@@ -107,12 +107,6 @@
     <t>BG(Modality)</t>
   </si>
   <si>
-    <t>销售区域</t>
-  </si>
-  <si>
-    <t xml:space="preserve">销售区域 </t>
-  </si>
-  <si>
     <t>医院编号</t>
   </si>
   <si>
@@ -137,9 +131,6 @@
     <t>进单日期</t>
   </si>
   <si>
-    <t>De-book原因</t>
-  </si>
-  <si>
     <t>Remark</t>
   </si>
   <si>
@@ -288,13 +279,22 @@
   </si>
   <si>
     <t>其他</t>
+  </si>
+  <si>
+    <t>销售区域-team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">销售区域-大区 </t>
+  </si>
+  <si>
+    <t>De-Book原因</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,12 +317,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -399,8 +393,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{D4598283-0CA3-4904-AF18-954A98422C47}"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -443,7 +437,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -773,40 +767,40 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -825,37 +819,37 @@
           <x14:formula1>
             <xm:f>Sheet2!$A$1:$A$17</xm:f>
           </x14:formula1>
-          <xm:sqref>A1:A1048576</xm:sqref>
+          <xm:sqref>A2:A1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0CFC432C-D4BF-431D-B15A-3E8CC5C1D104}">
           <x14:formula1>
             <xm:f>Sheet2!$B$1:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>B1:B1048576</xm:sqref>
+          <xm:sqref>B2:B1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2B19A510-2229-4608-A414-6DD8B1DDF494}">
           <x14:formula1>
             <xm:f>Sheet2!$C$1:$C$21</xm:f>
           </x14:formula1>
-          <xm:sqref>C1:C1048576</xm:sqref>
+          <xm:sqref>C2:C1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3BDD1278-FFAE-4E65-BB9E-7CA5BC99E2B6}">
           <x14:formula1>
             <xm:f>Sheet2!$D$1:$D$16</xm:f>
           </x14:formula1>
-          <xm:sqref>D1:D1048576</xm:sqref>
+          <xm:sqref>D2:D1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{506663EC-6732-4329-9339-13256FAF8A71}">
           <x14:formula1>
             <xm:f>Sheet2!$I$1:$I$2</xm:f>
           </x14:formula1>
-          <xm:sqref>I1:I1048576</xm:sqref>
+          <xm:sqref>I2:I1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E820F090-DBE4-400E-AE43-B61A8064CF3D}">
           <x14:formula1>
             <xm:f>Sheet2!$M$1:$M$7</xm:f>
           </x14:formula1>
-          <xm:sqref>M1:M1048576</xm:sqref>
+          <xm:sqref>M2:M1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -870,242 +864,242 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="C18" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="C19" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="C20" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="C21" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/template/De-Book Template.xlsx
+++ b/src/assets/template/De-Book Template.xlsx
@@ -11,9 +11,6 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
@@ -320,12 +317,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -338,6 +335,127 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -350,77 +468,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -432,9 +482,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -442,44 +491,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -517,37 +528,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -559,25 +636,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,43 +660,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -637,67 +672,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -727,6 +738,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -737,6 +763,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -756,26 +815,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -790,189 +834,156 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="44" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -985,17 +996,13 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="44" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="44" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="44" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="44" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1070,23 +1077,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Sheet3"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1347,11 +1337,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="6" max="6" width="18.9333333333333" customWidth="1"/>
-    <col min="12" max="12" width="9.875" style="5"/>
+    <col min="12" max="12" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" spans="1:14">
@@ -1388,7 +1377,7 @@
       <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
@@ -1397,102 +1386,6 @@
       <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J1">
@@ -1501,26 +1394,23 @@
   <conditionalFormatting sqref="K1:N1 A1:I1">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A7 B2:B7 C2:C7 D2:D7 I2:I7 M2:M7">
-      <formula1>[1]Sheet2!#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A8:A1048576">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1048576">
       <formula1>Sheet2!$A$1:$A$17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M8:M1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576">
       <formula1>Sheet2!$M$1:$M$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C8:C1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576">
       <formula1>Sheet2!$C$1:$C$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
       <formula1>Sheet2!$B$1:$B$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8:D1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
       <formula1>Sheet2!$D$1:$D$16</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8:I1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
       <formula1>Sheet2!$I$1:$I$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -1791,4 +1681,26 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <commentList sheetStid="1">
+    <comment s:ref="E1" rgbClr="99C954"/>
+    <comment s:ref="F1" rgbClr="99C954"/>
+    <comment s:ref="H1" rgbClr="99C954"/>
+    <comment s:ref="I1" rgbClr="99C954"/>
+    <comment s:ref="J1" rgbClr="99C954"/>
+    <comment s:ref="K1" rgbClr="99C954"/>
+  </commentList>
+</comments>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A0048C-2381-489B-AA07-9611017176EA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/src/assets/template/De-Book Template.xlsx
+++ b/src/assets/template/De-Book Template.xlsx
@@ -243,7 +243,7 @@
     <t>North2</t>
   </si>
   <si>
-    <t>其他场地问题</t>
+    <t>其它场地问题</t>
   </si>
   <si>
     <t>MR</t>
@@ -252,7 +252,7 @@
     <t>North1</t>
   </si>
   <si>
-    <t>其他</t>
+    <t>其它</t>
   </si>
   <si>
     <t>PDS-RadOnc</t>
@@ -322,7 +322,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -332,20 +332,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -837,149 +823,149 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -996,13 +982,13 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="44" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="44" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="44" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="44" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
